--- a/data/instances/WIP-FMS/instance_description.xlsx
+++ b/data/instances/WIP-FMS/instance_description.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,90 +429,115 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Heterogeneity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>BufferTightness</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Jobs</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Stages</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Machines/Stage</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>pt_low</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>pt_high</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>os_repeat</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>StageAvgPT</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>BufferCaps</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>QuickMakespan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>QuickBlocking</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>QuickBlockingRatio</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MultiAvgMakespan</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>MultiAvgBlocking</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>MultiAvgBlockingRatio</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>TuneIters</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>TuneStatus</t>
         </is>
@@ -531,62 +556,85 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>balanced</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>mild</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>55</v>
       </c>
-      <c r="E2" t="n">
+      <c r="J2" t="n">
         <v>20</v>
       </c>
-      <c r="F2" t="n">
+      <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
         <v>10</v>
       </c>
-      <c r="J2" t="n">
-        <v>120</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="n">
+        <v>120</v>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>[5.65, 5.475, 4.8]</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>[1, 1]</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="R2" t="n">
         <v>76</v>
       </c>
-      <c r="N2" t="n">
+      <c r="S2" t="n">
         <v>11</v>
       </c>
-      <c r="O2" t="n">
+      <c r="T2" t="n">
         <v>0.144737</v>
       </c>
-      <c r="P2" t="n">
+      <c r="U2" t="n">
         <v>74.333</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="V2" t="n">
         <v>7.667</v>
       </c>
-      <c r="R2" t="n">
+      <c r="W2" t="n">
         <v>0.102072</v>
       </c>
-      <c r="S2" t="n">
+      <c r="X2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -605,62 +653,85 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mid_bottleneck</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
-      </c>
-      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>34</v>
+      </c>
+      <c r="J3" t="n">
         <v>20</v>
       </c>
-      <c r="F3" t="n">
+      <c r="K3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="J3" t="n">
-        <v>120</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>[4.15, 12.7, 4.05]</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>[11, 7]</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>138</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
+        <v>120</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[6.15, 5.1, 6.425]</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>[1, 1]</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>80</v>
+      </c>
+      <c r="S3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.021739</v>
-      </c>
-      <c r="P3" t="n">
-        <v>131.333</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.043207</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="U3" t="n">
+        <v>77</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.112646</v>
+      </c>
+      <c r="X3" t="n">
         <v>14</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>max_iter</t>
         </is>
@@ -679,64 +750,87 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>downstream_bottleneck</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mid_bottleneck</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>tight</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>20</v>
       </c>
-      <c r="F4" t="n">
+      <c r="J4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" t="n">
-        <v>120</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>[3.375, 8.075, 9.85]</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>[9, 7]</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>113</v>
-      </c>
-      <c r="N4" t="n">
-        <v>6</v>
-      </c>
       <c r="O4" t="n">
-        <v>0.053097</v>
-      </c>
-      <c r="P4" t="n">
-        <v>108.333</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
+        <v>120</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[3.8, 10.575, 4.55]</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>[11, 11]</t>
+        </is>
       </c>
       <c r="R4" t="n">
-        <v>0.04831</v>
+        <v>99</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>hit</t>
+        <v>20</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.20202</v>
+      </c>
+      <c r="U4" t="n">
+        <v>106</v>
+      </c>
+      <c r="V4" t="n">
+        <v>17</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.161023</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>max_iter</t>
         </is>
       </c>
     </row>
@@ -753,62 +847,85 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>balanced</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>66</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>mild</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>68</v>
+      </c>
+      <c r="J5" t="n">
         <v>60</v>
       </c>
-      <c r="F5" t="n">
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" t="n">
-        <v>120</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>[5.094, 5.167, 5.45, 5.733, 5.928]</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>120</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[5.717, 5.267, 5.972, 5.533, 5.594]</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>[6, 6, 6, 6]</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>146</v>
-      </c>
-      <c r="N5" t="n">
-        <v>9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.061644</v>
-      </c>
-      <c r="P5" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.333</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.029792</v>
+        <v>152</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="U5" t="n">
+        <v>146.667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>14</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.09285499999999999</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -827,62 +944,85 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mid_bottleneck</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>77</v>
       </c>
-      <c r="E6" t="n">
+      <c r="J6" t="n">
         <v>60</v>
       </c>
-      <c r="F6" t="n">
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>120</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>[5.528, 5.394, 6.278, 5.928, 5.144]</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>[5, 5, 5, 5]</t>
-        </is>
-      </c>
       <c r="M6" t="n">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>0.067568</v>
-      </c>
-      <c r="P6" t="n">
-        <v>150.333</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>50</v>
+        <v>120</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[3.933, 7.261, 12.533, 8.05, 3.667]</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>[25, 25, 21, 21]</t>
+        </is>
       </c>
       <c r="R6" t="n">
-        <v>0.329678</v>
+        <v>258</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.073643</v>
+      </c>
+      <c r="U6" t="n">
+        <v>265</v>
+      </c>
+      <c r="V6" t="n">
+        <v>27.667</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.104351</v>
+      </c>
+      <c r="X6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -901,62 +1041,85 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>mid_bottleneck</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>44</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>mild</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>52</v>
+      </c>
+      <c r="J7" t="n">
         <v>60</v>
       </c>
-      <c r="F7" t="n">
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" t="n">
-        <v>120</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>[3.833, 7.994, 10.489, 7.833, 4.206]</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>[23, 18, 15, 15]</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>228</v>
-      </c>
-      <c r="N7" t="n">
-        <v>33</v>
-      </c>
       <c r="O7" t="n">
-        <v>0.144737</v>
-      </c>
-      <c r="P7" t="n">
-        <v>233.333</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>49.333</v>
+        <v>120</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>[5.444, 7.389, 8.367, 6.406, 5.061]</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>[11, 11, 9, 11]</t>
+        </is>
       </c>
       <c r="R7" t="n">
-        <v>0.211791</v>
+        <v>161</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.10559</v>
+      </c>
+      <c r="U7" t="n">
+        <v>166.333</v>
+      </c>
+      <c r="V7" t="n">
+        <v>22.667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.13364</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -975,62 +1138,85 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>mid_bottleneck</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>55</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>tight</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>58</v>
+      </c>
+      <c r="J8" t="n">
         <v>60</v>
       </c>
-      <c r="F8" t="n">
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
-        <v>120</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>[3.922, 8.278, 11.194, 7.694, 4.094]</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>[26, 25, 18, 18]</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>237</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20</v>
-      </c>
       <c r="O8" t="n">
-        <v>0.084388</v>
-      </c>
-      <c r="P8" t="n">
-        <v>239.667</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>25</v>
+        <v>120</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>[4.028, 8.122, 11.406, 9.128, 4.144]</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>[25, 25, 25, 25]</t>
+        </is>
       </c>
       <c r="R8" t="n">
-        <v>0.104573</v>
+        <v>219</v>
       </c>
       <c r="S8" t="n">
+        <v>13</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.059361</v>
+      </c>
+      <c r="U8" t="n">
+        <v>217</v>
+      </c>
+      <c r="V8" t="n">
+        <v>26</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.120596</v>
+      </c>
+      <c r="X8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -1049,64 +1235,87 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>downstream_bottleneck</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>26</v>
+      </c>
+      <c r="J9" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
+        <v>120</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>[3.35, 4.961, 8.061, 9.467, 10.117]</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>[18, 18, 18, 18]</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>231</v>
+      </c>
+      <c r="S9" t="n">
         <v>22</v>
       </c>
-      <c r="E9" t="n">
-        <v>60</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>120</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>[3.239, 4.883, 6.694, 9.228, 11.283]</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>[15, 15, 15, 11]</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>234</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.021368</v>
-      </c>
-      <c r="P9" t="n">
-        <v>247.667</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>71.667</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.286181</v>
-      </c>
-      <c r="S9" t="n">
-        <v>14</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>max_iter</t>
+      <c r="T9" t="n">
+        <v>0.095238</v>
+      </c>
+      <c r="U9" t="n">
+        <v>231</v>
+      </c>
+      <c r="V9" t="n">
+        <v>37.667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.162529</v>
+      </c>
+      <c r="X9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>hit</t>
         </is>
       </c>
     </row>
@@ -1123,64 +1332,87 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>downstream_bottleneck</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>33</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>tight</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>34</v>
+      </c>
+      <c r="J10" t="n">
         <v>60</v>
       </c>
-      <c r="F10" t="n">
+      <c r="K10" t="n">
         <v>5</v>
       </c>
-      <c r="G10" t="n">
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>120</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>[3.378, 5.583, 6.967, 9.894, 10.767]</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>[21, 18, 21, 18]</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>233</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20</v>
-      </c>
       <c r="O10" t="n">
-        <v>0.085837</v>
-      </c>
-      <c r="P10" t="n">
-        <v>240</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>11.667</v>
+        <v>120</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>[2.367, 4.75, 8.328, 11.194, 15.4]</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>[21, 21, 21, 21]</t>
+        </is>
       </c>
       <c r="R10" t="n">
-        <v>0.048815</v>
+        <v>283</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>hit</t>
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.028269</v>
+      </c>
+      <c r="U10" t="n">
+        <v>288</v>
+      </c>
+      <c r="V10" t="n">
+        <v>54.667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.190283</v>
+      </c>
+      <c r="X10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>max_iter</t>
         </is>
       </c>
     </row>
@@ -1197,62 +1429,85 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>downstream_bottleneck</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>44</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>48</v>
+      </c>
+      <c r="J11" t="n">
         <v>60</v>
       </c>
-      <c r="F11" t="n">
+      <c r="K11" t="n">
         <v>5</v>
       </c>
-      <c r="G11" t="n">
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
         <v>10</v>
       </c>
-      <c r="J11" t="n">
-        <v>120</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>[3.294, 5.678, 6.883, 9.6, 11.878]</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>[18, 15, 18, 15]</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>253</v>
-      </c>
-      <c r="N11" t="n">
-        <v>13</v>
-      </c>
       <c r="O11" t="n">
-        <v>0.051383</v>
-      </c>
-      <c r="P11" t="n">
-        <v>256</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>33.333</v>
+        <v>120</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>[2.422, 4.789, 9.694, 11.083, 14.967]</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>[25, 25, 25, 25]</t>
+        </is>
       </c>
       <c r="R11" t="n">
-        <v>0.130625</v>
+        <v>317</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
-      </c>
-      <c r="T11" t="inlineStr">
+        <v>40</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.126183</v>
+      </c>
+      <c r="U11" t="n">
+        <v>317.333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>46.333</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.146286</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -1271,64 +1526,87 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>balanced</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>88</v>
-      </c>
-      <c r="E12" t="n">
-        <v>120</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>mild</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>91</v>
+      </c>
+      <c r="J12" t="n">
+        <v>120</v>
+      </c>
+      <c r="K12" t="n">
         <v>8</v>
       </c>
-      <c r="G12" t="n">
+      <c r="L12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
         <v>10</v>
       </c>
-      <c r="J12" t="n">
-        <v>120</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>[5.865, 5.942, 6.002, 5.996, 5.508, 5.96, 6.21, 6.252]</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>[6, 6, 6, 6, 6, 6, 6]</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>235</v>
-      </c>
-      <c r="N12" t="n">
-        <v>46</v>
-      </c>
       <c r="O12" t="n">
-        <v>0.195745</v>
-      </c>
-      <c r="P12" t="n">
-        <v>233</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>35.667</v>
+        <v>120</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>[6.131, 5.792, 6.321, 6.398, 6.144, 6.054, 6.133, 6.731]</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>[8, 8, 8, 8, 8, 8, 8]</t>
+        </is>
       </c>
       <c r="R12" t="n">
-        <v>0.153552</v>
+        <v>248</v>
       </c>
       <c r="S12" t="n">
-        <v>14</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>max_iter</t>
+        <v>29</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.116935</v>
+      </c>
+      <c r="U12" t="n">
+        <v>247.333</v>
+      </c>
+      <c r="V12" t="n">
+        <v>21.333</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.08497200000000001</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>hit</t>
         </is>
       </c>
     </row>
@@ -1345,62 +1623,85 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
-      </c>
-      <c r="E13" t="n">
-        <v>120</v>
-      </c>
-      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>mid_bottleneck</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>102</v>
+      </c>
+      <c r="J13" t="n">
+        <v>120</v>
+      </c>
+      <c r="K13" t="n">
         <v>8</v>
       </c>
-      <c r="G13" t="n">
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
         <v>10</v>
       </c>
-      <c r="J13" t="n">
-        <v>120</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>[6.3, 5.769, 5.885, 6.381, 5.75, 5.871, 6.577, 5.963]</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>[4, 5, 5, 4, 5, 5, 4]</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>237</v>
-      </c>
-      <c r="N13" t="n">
-        <v>34</v>
-      </c>
       <c r="O13" t="n">
-        <v>0.14346</v>
-      </c>
-      <c r="P13" t="n">
-        <v>244</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>71</v>
+        <v>120</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>[4.04, 6.277, 7.869, 10.383, 11.481, 8.708, 6.252, 4.162]</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>[32, 32, 32, 32, 29, 29, 29]</t>
+        </is>
       </c>
       <c r="R13" t="n">
-        <v>0.290203</v>
+        <v>381</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.060367</v>
+      </c>
+      <c r="U13" t="n">
+        <v>375.333</v>
+      </c>
+      <c r="V13" t="n">
+        <v>42.667</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.11371</v>
+      </c>
+      <c r="X13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -1419,64 +1720,87 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>mid_bottleneck</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>66</v>
-      </c>
-      <c r="E14" t="n">
-        <v>120</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>mild</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>71</v>
+      </c>
+      <c r="J14" t="n">
+        <v>120</v>
+      </c>
+      <c r="K14" t="n">
         <v>8</v>
       </c>
-      <c r="G14" t="n">
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
         <v>10</v>
       </c>
-      <c r="J14" t="n">
-        <v>120</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>[3.806, 5.994, 8.044, 11.46, 11.213, 9.115, 6.892, 4.196]</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>[37, 37, 37, 33, 32, 32, 32]</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>382</v>
-      </c>
-      <c r="N14" t="n">
-        <v>124</v>
-      </c>
       <c r="O14" t="n">
-        <v>0.324607</v>
-      </c>
-      <c r="P14" t="n">
-        <v>389</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>55.667</v>
+        <v>120</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>[5.758, 7.552, 8.19, 8.844, 8.713, 8.346, 7.477, 5.862]</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>[23, 23, 23, 23, 23, 21, 21]</t>
+        </is>
       </c>
       <c r="R14" t="n">
-        <v>0.143129</v>
+        <v>276</v>
       </c>
       <c r="S14" t="n">
-        <v>14</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>max_iter</t>
+        <v>38</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.137681</v>
+      </c>
+      <c r="U14" t="n">
+        <v>272</v>
+      </c>
+      <c r="V14" t="n">
+        <v>34.667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.126675</v>
+      </c>
+      <c r="X14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>hit</t>
         </is>
       </c>
     </row>
@@ -1493,64 +1817,87 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>mid_bottleneck</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>tight</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>77</v>
       </c>
-      <c r="E15" t="n">
-        <v>120</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="J15" t="n">
+        <v>120</v>
+      </c>
+      <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="G15" t="n">
+      <c r="L15" t="n">
         <v>4</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>120</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>[4.165, 6.35, 8.304, 11.1, 10.767, 8.292, 6.556, 4.342]</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>[34, 32, 34, 32, 29, 29, 29]</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>361</v>
-      </c>
-      <c r="N15" t="n">
-        <v>32</v>
-      </c>
       <c r="O15" t="n">
-        <v>0.088643</v>
-      </c>
-      <c r="P15" t="n">
-        <v>376.667</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>30.667</v>
+        <v>120</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>[4.485, 6.794, 8.877, 11.829, 11.458, 8.865, 7.004, 4.698]</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>[33, 33, 33, 33, 33, 33, 33]</t>
+        </is>
       </c>
       <c r="R15" t="n">
-        <v>0.081313</v>
+        <v>335</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>hit</t>
+        <v>94</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.280597</v>
+      </c>
+      <c r="U15" t="n">
+        <v>336.667</v>
+      </c>
+      <c r="V15" t="n">
+        <v>56.333</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.168187</v>
+      </c>
+      <c r="X15" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>max_iter</t>
         </is>
       </c>
     </row>
@@ -1567,62 +1914,85 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mid_bottleneck</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>88</v>
-      </c>
-      <c r="E16" t="n">
-        <v>120</v>
-      </c>
-      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>downstream_bottleneck</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>99</v>
+      </c>
+      <c r="J16" t="n">
+        <v>120</v>
+      </c>
+      <c r="K16" t="n">
         <v>8</v>
       </c>
-      <c r="G16" t="n">
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
         <v>10</v>
       </c>
-      <c r="J16" t="n">
-        <v>120</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>[4.088, 6.333, 8.625, 10.825, 9.96, 8.529, 6.64, 4.354]</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>[34, 34, 32, 32, 29, 29, 29]</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>366</v>
-      </c>
-      <c r="N16" t="n">
-        <v>54</v>
-      </c>
       <c r="O16" t="n">
-        <v>0.147541</v>
-      </c>
-      <c r="P16" t="n">
-        <v>365.333</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>45.667</v>
+        <v>120</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>[3.794, 4.665, 5.885, 7.64, 8.006, 9.377, 11.865, 11.842]</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>[23, 23, 23, 23, 23, 23, 23]</t>
+        </is>
       </c>
       <c r="R16" t="n">
-        <v>0.124992</v>
+        <v>394</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
-      </c>
-      <c r="T16" t="inlineStr">
+        <v>31</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.07868</v>
+      </c>
+      <c r="U16" t="n">
+        <v>405.333</v>
+      </c>
+      <c r="V16" t="n">
+        <v>64.667</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.159225</v>
+      </c>
+      <c r="X16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -1641,64 +2011,87 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>downstream_bottleneck</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
-      </c>
-      <c r="E17" t="n">
-        <v>120</v>
-      </c>
-      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>mid_bottleneck</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>81</v>
+      </c>
+      <c r="J17" t="n">
+        <v>120</v>
+      </c>
+      <c r="K17" t="n">
         <v>8</v>
       </c>
-      <c r="G17" t="n">
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
         <v>10</v>
       </c>
-      <c r="J17" t="n">
-        <v>120</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>[3.404, 4.827, 6.662, 7.465, 8.694, 9.779, 9.844, 12.613]</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>[29, 29, 27, 27, 27, 27, 27]</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>404</v>
-      </c>
-      <c r="N17" t="n">
-        <v>55</v>
-      </c>
       <c r="O17" t="n">
-        <v>0.136139</v>
-      </c>
-      <c r="P17" t="n">
-        <v>406.333</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>60</v>
+        <v>120</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>[3.329, 6.308, 9.433, 13.546, 12.992, 9.865, 5.823, 2.812]</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>[40, 40, 40, 40, 40, 40, 40]</t>
+        </is>
       </c>
       <c r="R17" t="n">
-        <v>0.147617</v>
+        <v>435</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>hit</t>
+        <v>101</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.232184</v>
+      </c>
+      <c r="U17" t="n">
+        <v>446.667</v>
+      </c>
+      <c r="V17" t="n">
+        <v>85</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.190584</v>
+      </c>
+      <c r="X17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>stuck</t>
         </is>
       </c>
     </row>
@@ -1715,62 +2108,85 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>downstream_bottleneck</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>66</v>
-      </c>
-      <c r="E18" t="n">
-        <v>120</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>tight</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>68</v>
+      </c>
+      <c r="J18" t="n">
+        <v>120</v>
+      </c>
+      <c r="K18" t="n">
         <v>8</v>
       </c>
-      <c r="G18" t="n">
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
-        <v>120</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>[3.306, 4.523, 5.6, 7.56, 8.654, 10.135, 11.648, 12.067]</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>[29, 27, 29, 27, 27, 27, 27]</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>403</v>
-      </c>
-      <c r="N18" t="n">
-        <v>47</v>
-      </c>
       <c r="O18" t="n">
-        <v>0.116625</v>
-      </c>
-      <c r="P18" t="n">
-        <v>402</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>19.667</v>
+        <v>120</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>[2.867, 4.673, 6.427, 8.129, 9.875, 11.798, 13.265, 14.573]</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>[29, 29, 29, 29, 29, 29, 29]</t>
+        </is>
       </c>
       <c r="R18" t="n">
-        <v>0.048842</v>
+        <v>385</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
-      </c>
-      <c r="T18" t="inlineStr">
+        <v>57</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.148052</v>
+      </c>
+      <c r="U18" t="n">
+        <v>392</v>
+      </c>
+      <c r="V18" t="n">
+        <v>58.667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.150535</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -1789,62 +2205,85 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>downstream_bottleneck</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>77</v>
-      </c>
-      <c r="E19" t="n">
-        <v>120</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>80</v>
+      </c>
+      <c r="J19" t="n">
+        <v>120</v>
+      </c>
+      <c r="K19" t="n">
         <v>8</v>
       </c>
-      <c r="G19" t="n">
+      <c r="L19" t="n">
         <v>4</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
         <v>10</v>
       </c>
-      <c r="J19" t="n">
-        <v>120</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>[3.583, 4.785, 5.785, 7.344, 8.306, 9.227, 11.054, 12.479]</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>[25, 23, 23, 23, 23, 23, 23]</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>394</v>
-      </c>
-      <c r="N19" t="n">
-        <v>51</v>
-      </c>
       <c r="O19" t="n">
-        <v>0.129442</v>
-      </c>
-      <c r="P19" t="n">
-        <v>395.667</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>34.333</v>
+        <v>120</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>[2.562, 4.14, 5.885, 7.698, 9.46, 10.627, 13.073, 13.935]</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>[32, 32, 32, 32, 32, 32, 32]</t>
+        </is>
       </c>
       <c r="R19" t="n">
-        <v>0.08687499999999999</v>
+        <v>431</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
-      </c>
-      <c r="T19" t="inlineStr">
+        <v>54</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.12529</v>
+      </c>
+      <c r="U19" t="n">
+        <v>455.333</v>
+      </c>
+      <c r="V19" t="n">
+        <v>71</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.155992</v>
+      </c>
+      <c r="X19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -1863,62 +2302,85 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>downstream_bottleneck</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>88</v>
-      </c>
-      <c r="E20" t="n">
-        <v>120</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>tight</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>96</v>
+      </c>
+      <c r="J20" t="n">
+        <v>120</v>
+      </c>
+      <c r="K20" t="n">
         <v>8</v>
       </c>
-      <c r="G20" t="n">
+      <c r="L20" t="n">
         <v>4</v>
       </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
         <v>10</v>
       </c>
-      <c r="J20" t="n">
-        <v>120</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>[3.567, 4.775, 6.002, 7.173, 7.708, 9.498, 11.135, 12.46]</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>[27, 26, 26, 26, 26, 26, 26]</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>395</v>
-      </c>
-      <c r="N20" t="n">
-        <v>23</v>
-      </c>
       <c r="O20" t="n">
-        <v>0.058228</v>
-      </c>
-      <c r="P20" t="n">
-        <v>412.667</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>15</v>
+        <v>120</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>[2.415, 3.89, 6.062, 7.99, 9.602, 10.942, 11.887, 13.971]</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>[34, 34, 34, 34, 34, 34, 34]</t>
+        </is>
       </c>
       <c r="R20" t="n">
-        <v>0.036367</v>
+        <v>452</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
-      </c>
-      <c r="T20" t="inlineStr">
+        <v>54</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.119469</v>
+      </c>
+      <c r="U20" t="n">
+        <v>440.667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>85.667</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.194429</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
@@ -1937,62 +2399,85 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>downstream_bottleneck</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>99</v>
-      </c>
-      <c r="E21" t="n">
-        <v>120</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>tight</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>107</v>
+      </c>
+      <c r="J21" t="n">
+        <v>120</v>
+      </c>
+      <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="G21" t="n">
+      <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="J21" t="n">
-        <v>120</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>[3.794, 4.665, 5.885, 7.64, 8.006, 9.377, 11.865, 11.842]</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>[23, 23, 23, 23, 23, 23, 23]</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
-        <v>394</v>
-      </c>
-      <c r="N21" t="n">
-        <v>31</v>
-      </c>
       <c r="O21" t="n">
-        <v>0.07868</v>
-      </c>
-      <c r="P21" t="n">
-        <v>405.333</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>64.667</v>
+        <v>120</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>[3.663, 5.142, 6.048, 7.885, 9.833, 10.592, 10.658, 12.475]</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>[24, 24, 24, 24, 24, 24, 24]</t>
+        </is>
       </c>
       <c r="R21" t="n">
-        <v>0.159225</v>
+        <v>338</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
-      </c>
-      <c r="T21" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.142012</v>
+      </c>
+      <c r="U21" t="n">
+        <v>342.333</v>
+      </c>
+      <c r="V21" t="n">
+        <v>67.333</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.19763</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
